--- a/encomendas_a_editora/encomenda_editora_2026-07-08.xlsx
+++ b/encomendas_a_editora/encomenda_editora_2026-07-08.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>ISBN do manual</t>
   </si>
@@ -57,33 +57,6 @@
   </si>
   <si>
     <t>VAMOS praticar + (Livro de Fichas) - Estudo do Meio - 1.º Ano</t>
-  </si>
-  <si>
-    <t>MISSÃO Zupi - Português - 3.º Ano</t>
-  </si>
-  <si>
-    <t>Livro de Fichas - MISSÃO Zupi - Português - 3.º Ano</t>
-  </si>
-  <si>
-    <t>MISSÃO Zupi - Matemática - 3.º Ano</t>
-  </si>
-  <si>
-    <t>Livro de Fichas - MISSÃO Zupi - Matemática - 3.º Ano</t>
-  </si>
-  <si>
-    <t>MISSÃO Zupi - Estudo do Meio - 3.º Ano</t>
-  </si>
-  <si>
-    <t>Livro de Fichas - MISSÃO Zupi - Estudo do Meio - 3.º Ano</t>
-  </si>
-  <si>
-    <t>Start the Magic! 3</t>
-  </si>
-  <si>
-    <t>Leya Editora</t>
-  </si>
-  <si>
-    <t>Start the Magic! 3 - Workbook</t>
   </si>
 </sst>
 </file>
@@ -136,7 +109,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G7"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
@@ -296,174 +269,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2">
-        <v>9789720112590</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8"/>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="3">
-        <v>12.26</v>
-      </c>
-      <c r="G8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2">
-        <v>9789720112606</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9"/>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="3">
-        <v>13.25</v>
-      </c>
-      <c r="G9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2">
-        <v>9789720132413</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10">
-        <v>2</v>
-      </c>
-      <c r="D10"/>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="3">
-        <v>12.18</v>
-      </c>
-      <c r="G10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2">
-        <v>9789720132420</v>
-      </c>
-      <c r="B11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11"/>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="3">
-        <v>13.25</v>
-      </c>
-      <c r="G11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2">
-        <v>9789720123138</v>
-      </c>
-      <c r="B12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12"/>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="3">
-        <v>12.29</v>
-      </c>
-      <c r="G12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2">
-        <v>9789720123145</v>
-      </c>
-      <c r="B13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13"/>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="3">
-        <v>13.05</v>
-      </c>
-      <c r="G13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2">
-        <v>9789724757261</v>
-      </c>
-      <c r="B14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14"/>
-      <c r="E14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="3">
-        <v>12.23</v>
-      </c>
-      <c r="G14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2">
-        <v>9789724757278</v>
-      </c>
-      <c r="B15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15"/>
-      <c r="E15" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" s="3">
-        <v>13.08</v>
-      </c>
-      <c r="G15" t="s">
-        <v>11</v>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>